--- a/survey/references/OD_nationale_quebec_2025.xlsx
+++ b/survey/references/OD_nationale_quebec_2025.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="1395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2353" uniqueCount="1390">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -1283,16 +1283,10 @@
     <t xml:space="preserve">Please select this place from the list of previously located places:</t>
   </si>
   <si>
-    <t xml:space="preserve">Custom because of the choices</t>
-  </si>
-  <si>
     <t xml:space="preserve">visitedPlaceName</t>
   </si>
   <si>
     <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custom until Evolution supports shortcuts</t>
   </si>
   <si>
     <t xml:space="preserve">visitedPlaceGeography</t>
@@ -1327,9 +1321,6 @@
     <t xml:space="preserve">At what time did you leave the previous location ({{visitedPlaceDescription}}) before going to your usual work place?</t>
   </si>
   <si>
-    <t xml:space="preserve">Custom because of the complexity of the widget, implying moving activities</t>
-  </si>
-  <si>
     <t xml:space="preserve">visitedPlacePreviousArrivalTime</t>
   </si>
   <si>
@@ -1358,9 +1349,6 @@
   </si>
   <si>
     <t xml:space="preserve">You arrived {{atPlace}} at:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custom because it’s a time widget, not supported by generator</t>
   </si>
   <si>
     <t xml:space="preserve">visitedPlaceNextPlaceCategory</t>
@@ -1413,9 +1401,6 @@
   </si>
   <si>
     <t xml:space="preserve">Confirm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custom because they are action button, but not to go to next section</t>
   </si>
   <si>
     <t xml:space="preserve">buttonCancelVisitedPlace</t>
@@ -5974,8 +5959,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="19.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="35.05"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16357" min="25" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16358" min="16358" style="0" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16359" style="2" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16358" style="2" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6051,7 +6035,7 @@
       <c r="X1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="XED1" s="0"/>
+      <c r="XED1" s="2"/>
       <c r="XEE1" s="2"/>
       <c r="XEF1" s="2"/>
       <c r="XEG1" s="2"/>
@@ -6834,7 +6818,7 @@
       <c r="U17" s="8"/>
       <c r="V17" s="8"/>
       <c r="W17" s="8"/>
-      <c r="XED17" s="0"/>
+      <c r="XED17" s="2"/>
       <c r="XEE17" s="2"/>
       <c r="XEF17" s="2"/>
       <c r="XEG17" s="2"/>
@@ -8771,7 +8755,6 @@
       <c r="U57" s="30"/>
       <c r="V57" s="30"/>
       <c r="W57" s="30"/>
-      <c r="XED57" s="0"/>
     </row>
     <row r="58" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
@@ -9115,7 +9098,7 @@
         <v>359</v>
       </c>
       <c r="B66" s="28" t="s">
-        <v>33</v>
+        <v>276</v>
       </c>
       <c r="C66" s="29" t="n">
         <f aca="false">TRUE()</f>
@@ -9168,7 +9151,7 @@
         <v>366</v>
       </c>
       <c r="B67" s="28" t="s">
-        <v>72</v>
+        <v>276</v>
       </c>
       <c r="C67" s="29" t="n">
         <f aca="false">TRUE()</f>
@@ -9204,16 +9187,13 @@
       <c r="U67" s="30"/>
       <c r="V67" s="30"/>
       <c r="W67" s="30"/>
-      <c r="X67" s="1" t="s">
-        <v>370</v>
-      </c>
     </row>
     <row r="68" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B68" s="28" t="s">
-        <v>72</v>
+        <v>276</v>
       </c>
       <c r="C68" s="29" t="n">
         <f aca="false">TRUE()</f>
@@ -9226,7 +9206,7 @@
         <v>339</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G68" s="10"/>
       <c r="H68" s="33"/>
@@ -9245,16 +9225,13 @@
       <c r="U68" s="30"/>
       <c r="V68" s="30"/>
       <c r="W68" s="30"/>
-      <c r="X68" s="1" t="s">
-        <v>373</v>
-      </c>
     </row>
     <row r="69" customFormat="false" ht="116.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B69" s="28" t="s">
-        <v>72</v>
+        <v>276</v>
       </c>
       <c r="C69" s="29" t="n">
         <f aca="false">TRUE()</f>
@@ -9267,13 +9244,13 @@
         <v>339</v>
       </c>
       <c r="F69" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>375</v>
-      </c>
-      <c r="G69" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>377</v>
       </c>
       <c r="I69" s="28"/>
       <c r="J69" s="28"/>
@@ -9290,16 +9267,13 @@
       <c r="U69" s="30"/>
       <c r="V69" s="30"/>
       <c r="W69" s="30"/>
-      <c r="X69" s="1" t="s">
-        <v>373</v>
-      </c>
     </row>
     <row r="70" customFormat="false" ht="87.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B70" s="28" t="s">
-        <v>72</v>
+        <v>276</v>
       </c>
       <c r="C70" s="29" t="n">
         <f aca="false">TRUE()</f>
@@ -9312,19 +9286,19 @@
         <v>339</v>
       </c>
       <c r="F70" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="H70" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="G70" s="10" t="s">
+      <c r="I70" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="H70" s="10" t="s">
+      <c r="J70" s="10" t="s">
         <v>381</v>
-      </c>
-      <c r="I70" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="J70" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="K70" s="28"/>
       <c r="L70" s="30"/>
@@ -9339,16 +9313,13 @@
       <c r="U70" s="30"/>
       <c r="V70" s="30"/>
       <c r="W70" s="30"/>
-      <c r="X70" s="1" t="s">
-        <v>384</v>
-      </c>
     </row>
     <row r="71" customFormat="false" ht="40.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B71" s="28" t="s">
-        <v>72</v>
+        <v>276</v>
       </c>
       <c r="C71" s="29" t="n">
         <f aca="false">TRUE()</f>
@@ -9361,7 +9332,7 @@
         <v>339</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="G71" s="10"/>
       <c r="H71" s="33"/>
@@ -9380,16 +9351,13 @@
       <c r="U71" s="30"/>
       <c r="V71" s="30"/>
       <c r="W71" s="30"/>
-      <c r="X71" s="1" t="s">
-        <v>384</v>
-      </c>
     </row>
     <row r="72" customFormat="false" ht="39.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B72" s="28" t="s">
-        <v>72</v>
+        <v>276</v>
       </c>
       <c r="C72" s="29" t="n">
         <f aca="false">TRUE()</f>
@@ -9402,7 +9370,7 @@
         <v>339</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="G72" s="10"/>
       <c r="H72" s="33"/>
@@ -9421,16 +9389,13 @@
       <c r="U72" s="30"/>
       <c r="V72" s="30"/>
       <c r="W72" s="30"/>
-      <c r="X72" s="1" t="s">
-        <v>384</v>
-      </c>
     </row>
     <row r="73" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B73" s="28" t="s">
-        <v>72</v>
+        <v>276</v>
       </c>
       <c r="C73" s="29" t="n">
         <f aca="false">TRUE()</f>
@@ -9443,19 +9408,19 @@
         <v>339</v>
       </c>
       <c r="F73" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="I73" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="G73" s="10" t="s">
+      <c r="J73" s="10" t="s">
         <v>391</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="I73" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="J73" s="10" t="s">
-        <v>394</v>
       </c>
       <c r="K73" s="28"/>
       <c r="L73" s="30"/>
@@ -9470,13 +9435,10 @@
       <c r="U73" s="30"/>
       <c r="V73" s="30"/>
       <c r="W73" s="30"/>
-      <c r="X73" s="1" t="s">
-        <v>395</v>
-      </c>
     </row>
     <row r="74" customFormat="false" ht="131.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B74" s="28" t="s">
         <v>276</v>
@@ -9492,19 +9454,19 @@
         <v>339</v>
       </c>
       <c r="F74" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="I74" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="J74" s="10" t="s">
         <v>397</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="H74" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="I74" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="J74" s="10" t="s">
-        <v>401</v>
       </c>
       <c r="K74" s="28"/>
       <c r="L74" s="30"/>
@@ -9522,10 +9484,10 @@
     </row>
     <row r="75" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B75" s="28" t="s">
-        <v>72</v>
+        <v>276</v>
       </c>
       <c r="C75" s="29" t="n">
         <f aca="false">TRUE()</f>
@@ -9538,19 +9500,19 @@
         <v>339</v>
       </c>
       <c r="F75" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="J75" s="10" t="s">
         <v>403</v>
-      </c>
-      <c r="G75" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="I75" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="J75" s="10" t="s">
-        <v>407</v>
       </c>
       <c r="K75" s="28"/>
       <c r="L75" s="30"/>
@@ -9565,16 +9527,13 @@
       <c r="U75" s="30"/>
       <c r="V75" s="30"/>
       <c r="W75" s="30"/>
-      <c r="X75" s="1" t="s">
-        <v>395</v>
-      </c>
     </row>
     <row r="76" customFormat="false" ht="40.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B76" s="28" t="s">
-        <v>72</v>
+        <v>276</v>
       </c>
       <c r="C76" s="29" t="n">
         <f aca="false">TRUE()</f>
@@ -9587,13 +9546,13 @@
         <v>339</v>
       </c>
       <c r="F76" s="30" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="H76" s="33" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="I76" s="28"/>
       <c r="J76" s="28"/>
@@ -9610,16 +9569,13 @@
       <c r="U76" s="30"/>
       <c r="V76" s="30"/>
       <c r="W76" s="30"/>
-      <c r="X76" s="1" t="s">
-        <v>412</v>
-      </c>
     </row>
     <row r="77" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B77" s="28" t="s">
-        <v>72</v>
+        <v>276</v>
       </c>
       <c r="C77" s="29" t="n">
         <f aca="false">TRUE()</f>
@@ -9649,16 +9605,13 @@
       <c r="U77" s="30"/>
       <c r="V77" s="30"/>
       <c r="W77" s="30"/>
-      <c r="X77" s="1" t="s">
-        <v>412</v>
-      </c>
     </row>
     <row r="78" customFormat="false" ht="41.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B78" s="28" t="s">
-        <v>72</v>
+        <v>276</v>
       </c>
       <c r="C78" s="29" t="n">
         <f aca="false">TRUE()</f>
@@ -9688,13 +9641,10 @@
       <c r="U78" s="30"/>
       <c r="V78" s="30"/>
       <c r="W78" s="30"/>
-      <c r="X78" s="1" t="s">
-        <v>412</v>
-      </c>
     </row>
     <row r="79" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B79" s="28" t="s">
         <v>276</v>
@@ -9708,20 +9658,20 @@
       </c>
       <c r="E79" s="30"/>
       <c r="F79" s="30" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I79" s="28"/>
       <c r="J79" s="28"/>
       <c r="K79" s="28"/>
       <c r="L79" s="30"/>
       <c r="M79" s="30" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="N79" s="30"/>
       <c r="O79" s="30"/>
@@ -9746,7 +9696,7 @@
         <v>1</v>
       </c>
       <c r="D80" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E80" s="30"/>
       <c r="F80" s="30"/>
@@ -9770,7 +9720,6 @@
       <c r="U80" s="30"/>
       <c r="V80" s="30"/>
       <c r="W80" s="30"/>
-      <c r="XED80" s="0"/>
     </row>
     <row r="81" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
@@ -9784,7 +9733,7 @@
         <v>1</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E81" s="30"/>
       <c r="F81" s="30" t="s">
@@ -9814,7 +9763,7 @@
     </row>
     <row r="82" customFormat="false" ht="29.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B82" s="28" t="s">
         <v>276</v>
@@ -9824,23 +9773,23 @@
         <v>1</v>
       </c>
       <c r="D82" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E82" s="30"/>
       <c r="F82" s="10" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="K82" s="28"/>
       <c r="L82" s="30"/>
@@ -9871,11 +9820,11 @@
         <v>1</v>
       </c>
       <c r="D83" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E83" s="30"/>
       <c r="F83" s="10" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="G83" s="10" t="s">
         <v>336</v>
@@ -9884,7 +9833,7 @@
         <v>337</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="J83" s="34" t="s">
         <v>338</v>
@@ -9905,7 +9854,7 @@
     </row>
     <row r="84" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B84" s="28" t="s">
         <v>276</v>
@@ -9915,11 +9864,11 @@
         <v>1</v>
       </c>
       <c r="D84" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E84" s="30"/>
       <c r="F84" s="10" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="G84" s="10"/>
       <c r="H84" s="33"/>
@@ -9941,7 +9890,7 @@
     </row>
     <row r="85" customFormat="false" ht="38.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B85" s="28" t="s">
         <v>276</v>
@@ -9951,19 +9900,19 @@
         <v>1</v>
       </c>
       <c r="D85" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E85" s="30" t="s">
+        <v>423</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>428</v>
-      </c>
-      <c r="F85" s="10" t="s">
-        <v>431</v>
-      </c>
-      <c r="G85" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>433</v>
       </c>
       <c r="I85" s="28"/>
       <c r="J85" s="28"/>
@@ -9983,7 +9932,7 @@
     </row>
     <row r="86" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B86" s="28" t="s">
         <v>276</v>
@@ -9993,19 +9942,19 @@
         <v>1</v>
       </c>
       <c r="D86" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E86" s="30" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="H86" s="33" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="I86" s="28"/>
       <c r="J86" s="28"/>
@@ -10025,7 +9974,7 @@
     </row>
     <row r="87" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B87" s="28" t="s">
         <v>276</v>
@@ -10035,13 +9984,13 @@
         <v>1</v>
       </c>
       <c r="D87" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E87" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="G87" s="10"/>
       <c r="H87" s="33"/>
@@ -10063,7 +10012,7 @@
     </row>
     <row r="88" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B88" s="28" t="s">
         <v>276</v>
@@ -10073,13 +10022,13 @@
         <v>1</v>
       </c>
       <c r="D88" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E88" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F88" s="10" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G88" s="10"/>
       <c r="H88" s="33"/>
@@ -10101,7 +10050,7 @@
     </row>
     <row r="89" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B89" s="28" t="s">
         <v>276</v>
@@ -10111,13 +10060,13 @@
         <v>1</v>
       </c>
       <c r="D89" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E89" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="G89" s="10"/>
       <c r="H89" s="33"/>
@@ -10139,7 +10088,7 @@
     </row>
     <row r="90" customFormat="false" ht="102.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="10" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B90" s="28" t="s">
         <v>72</v>
@@ -10149,25 +10098,25 @@
         <v>1</v>
       </c>
       <c r="D90" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E90" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="J90" s="14" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="K90" s="14"/>
       <c r="L90" s="30"/>
@@ -10183,12 +10132,12 @@
       <c r="V90" s="30"/>
       <c r="W90" s="30"/>
       <c r="X90" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="37.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B91" s="28" t="s">
         <v>33</v>
@@ -10198,26 +10147,26 @@
         <v>1</v>
       </c>
       <c r="D91" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E91" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="I91" s="14"/>
       <c r="J91" s="14"/>
       <c r="K91" s="14"/>
       <c r="L91" s="30"/>
       <c r="M91" s="30" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="N91" s="30"/>
       <c r="O91" s="30" t="s">
@@ -10237,7 +10186,7 @@
     </row>
     <row r="92" customFormat="false" ht="32.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B92" s="28" t="s">
         <v>82</v>
@@ -10247,28 +10196,28 @@
         <v>1</v>
       </c>
       <c r="D92" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E92" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="I92" s="14"/>
       <c r="J92" s="14"/>
       <c r="K92" s="8" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="L92" s="30"/>
       <c r="M92" s="30" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="N92" s="30"/>
       <c r="O92" s="30"/>
@@ -10286,7 +10235,7 @@
     </row>
     <row r="93" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B93" s="28" t="s">
         <v>276</v>
@@ -10296,19 +10245,19 @@
         <v>1</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E93" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="G93" s="35" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="I93" s="14"/>
       <c r="J93" s="14"/>
@@ -10331,7 +10280,7 @@
     </row>
     <row r="94" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B94" s="28" t="s">
         <v>72</v>
@@ -10341,19 +10290,19 @@
         <v>1</v>
       </c>
       <c r="D94" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E94" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="I94" s="14"/>
       <c r="J94" s="14"/>
@@ -10374,12 +10323,12 @@
       <c r="V94" s="30"/>
       <c r="W94" s="30"/>
       <c r="X94" s="1" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="33.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="10" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B95" s="28" t="s">
         <v>72</v>
@@ -10389,19 +10338,19 @@
         <v>1</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E95" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="I95" s="14"/>
       <c r="J95" s="14"/>
@@ -10422,12 +10371,12 @@
       <c r="V95" s="30"/>
       <c r="W95" s="30"/>
       <c r="X95" s="1" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B96" s="28" t="s">
         <v>33</v>
@@ -10437,30 +10386,30 @@
         <v>1</v>
       </c>
       <c r="D96" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E96" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="I96" s="14"/>
       <c r="J96" s="14"/>
       <c r="K96" s="14"/>
       <c r="L96" s="30"/>
       <c r="M96" s="10" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="N96" s="30"/>
       <c r="O96" s="30" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="P96" s="30"/>
       <c r="Q96" s="30"/>
@@ -10476,7 +10425,7 @@
     </row>
     <row r="97" customFormat="false" ht="48.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B97" s="28" t="s">
         <v>25</v>
@@ -10486,29 +10435,29 @@
         <v>1</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E97" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="I97" s="14"/>
       <c r="J97" s="14"/>
       <c r="K97" s="14"/>
       <c r="L97" s="30"/>
       <c r="M97" s="30" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="N97" s="30" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="O97" s="30"/>
       <c r="P97" s="30"/>
@@ -10525,7 +10474,7 @@
     </row>
     <row r="98" customFormat="false" ht="39.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B98" s="28" t="s">
         <v>72</v>
@@ -10535,19 +10484,19 @@
         <v>1</v>
       </c>
       <c r="D98" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E98" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="I98" s="14"/>
       <c r="J98" s="14"/>
@@ -10565,12 +10514,12 @@
       <c r="V98" s="30"/>
       <c r="W98" s="30"/>
       <c r="X98" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B99" s="28" t="s">
         <v>276</v>
@@ -10580,10 +10529,10 @@
         <v>1</v>
       </c>
       <c r="D99" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E99" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F99" s="10"/>
       <c r="G99" s="10"/>
@@ -10606,7 +10555,7 @@
     </row>
     <row r="100" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="10" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B100" s="28" t="s">
         <v>276</v>
@@ -10616,19 +10565,19 @@
         <v>1</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="I100" s="14"/>
       <c r="J100" s="14"/>
@@ -10648,7 +10597,7 @@
     </row>
     <row r="101" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="10" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B101" s="28" t="s">
         <v>276</v>
@@ -10658,24 +10607,24 @@
         <v>1</v>
       </c>
       <c r="D101" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E101" s="30"/>
       <c r="F101" s="30" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I101" s="14"/>
       <c r="J101" s="14"/>
       <c r="K101" s="14"/>
       <c r="L101" s="30"/>
       <c r="M101" s="30" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="N101" s="30"/>
       <c r="O101" s="30"/>
@@ -10700,7 +10649,7 @@
         <v>1</v>
       </c>
       <c r="D102" s="28" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E102" s="30"/>
       <c r="F102" s="30"/>
@@ -10725,9 +10674,8 @@
       <c r="V102" s="30"/>
       <c r="W102" s="30"/>
       <c r="X102" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="XED102" s="0"/>
+        <v>493</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="s">
@@ -10741,7 +10689,7 @@
         <v>1</v>
       </c>
       <c r="D103" s="28" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E103" s="30"/>
       <c r="F103" s="30" t="s">
@@ -10769,12 +10717,12 @@
       <c r="V103" s="30"/>
       <c r="W103" s="30"/>
       <c r="X103" s="1" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="10" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B104" s="28" t="s">
         <v>72</v>
@@ -10784,17 +10732,17 @@
         <v>1</v>
       </c>
       <c r="D104" s="28" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E104" s="30"/>
       <c r="F104" s="30" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="I104" s="14"/>
       <c r="J104" s="14"/>
@@ -10815,45 +10763,45 @@
       <c r="V104" s="30"/>
       <c r="W104" s="30"/>
       <c r="X104" s="1" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="10" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B105" s="28" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C105" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D105" s="28" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E105" s="30"/>
       <c r="F105" s="10" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="I105" s="14"/>
       <c r="J105" s="14"/>
       <c r="K105" s="14"/>
       <c r="L105" s="30"/>
       <c r="M105" s="30" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="N105" s="30" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="O105" s="30" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="P105" s="30"/>
       <c r="Q105" s="30"/>
@@ -10866,7 +10814,7 @@
     </row>
     <row r="106" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B106" s="28" t="s">
         <v>72</v>
@@ -10876,31 +10824,31 @@
         <v>1</v>
       </c>
       <c r="D106" s="28" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E106" s="30"/>
       <c r="F106" s="10" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="K106" s="14"/>
       <c r="L106" s="30"/>
       <c r="M106" s="30" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="N106" s="30" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="O106" s="30"/>
       <c r="P106" s="30"/>
@@ -10915,12 +10863,12 @@
       <c r="V106" s="30"/>
       <c r="W106" s="30"/>
       <c r="X106" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="10" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B107" s="28" t="s">
         <v>72</v>
@@ -10930,17 +10878,17 @@
         <v>1</v>
       </c>
       <c r="D107" s="28" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E107" s="30"/>
       <c r="F107" s="30" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="I107" s="14"/>
       <c r="J107" s="14"/>
@@ -10961,45 +10909,45 @@
       <c r="V107" s="30"/>
       <c r="W107" s="30"/>
       <c r="X107" s="1" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="B108" s="28" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C108" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D108" s="28" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E108" s="30"/>
       <c r="F108" s="10" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="I108" s="14"/>
       <c r="J108" s="14"/>
       <c r="K108" s="14"/>
       <c r="L108" s="30"/>
       <c r="M108" s="30" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="N108" s="30" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="O108" s="30" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="P108" s="30"/>
       <c r="Q108" s="30"/>
@@ -11012,7 +10960,7 @@
     </row>
     <row r="109" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="10" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="B109" s="28" t="s">
         <v>72</v>
@@ -11022,31 +10970,31 @@
         <v>1</v>
       </c>
       <c r="D109" s="28" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E109" s="30"/>
       <c r="F109" s="10" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="K109" s="2"/>
       <c r="L109" s="30"/>
       <c r="M109" s="30" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="N109" s="30" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="O109" s="30"/>
       <c r="P109" s="30"/>
@@ -11061,12 +11009,12 @@
       <c r="V109" s="30"/>
       <c r="W109" s="30"/>
       <c r="X109" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B110" s="28" t="s">
         <v>103</v>
@@ -11076,11 +11024,11 @@
         <v>1</v>
       </c>
       <c r="D110" s="28" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E110" s="30"/>
       <c r="F110" s="30" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="G110" s="28" t="s">
         <v>323</v>
@@ -11106,7 +11054,7 @@
     </row>
     <row r="111" customFormat="false" ht="77.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="B111" s="28" t="s">
         <v>33</v>
@@ -11116,23 +11064,23 @@
         <v>1</v>
       </c>
       <c r="D111" s="34" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E111" s="30"/>
       <c r="F111" s="10" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="G111" s="36" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="H111" s="36" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="I111" s="37" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="J111" s="36" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="K111" s="30"/>
       <c r="L111" s="30"/>
@@ -11155,7 +11103,7 @@
     </row>
     <row r="112" s="2" customFormat="true" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="38" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B112" s="38" t="s">
         <v>72</v>
@@ -11165,7 +11113,7 @@
         <v>1</v>
       </c>
       <c r="D112" s="34" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E112" s="39"/>
       <c r="F112" s="38" t="str">
@@ -11185,13 +11133,12 @@
         <v>1</v>
       </c>
       <c r="X112" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="XED112" s="0"/>
+        <v>539</v>
+      </c>
     </row>
     <row r="113" s="2" customFormat="true" ht="67.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="38" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B113" s="28" t="s">
         <v>33</v>
@@ -11201,42 +11148,41 @@
         <v>1</v>
       </c>
       <c r="D113" s="34" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E113" s="39"/>
       <c r="F113" s="38" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G113" s="40" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="H113" s="42" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="I113" s="40" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="J113" s="42" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
       <c r="M113" s="1" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="N113" s="1"/>
       <c r="O113" s="2" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="S113" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="XED113" s="0"/>
     </row>
     <row r="114" s="2" customFormat="true" ht="54.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="38" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="B114" s="28" t="s">
         <v>33</v>
@@ -11246,42 +11192,41 @@
         <v>1</v>
       </c>
       <c r="D114" s="34" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E114" s="39"/>
       <c r="F114" s="38" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="G114" s="40" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="H114" s="42" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="I114" s="40" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="J114" s="42" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="K114" s="1"/>
       <c r="L114" s="1"/>
       <c r="M114" s="1" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="N114" s="1"/>
       <c r="O114" s="2" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="S114" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="XED114" s="0"/>
     </row>
     <row r="115" s="2" customFormat="true" ht="54.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="38" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B115" s="28" t="s">
         <v>33</v>
@@ -11291,42 +11236,41 @@
         <v>1</v>
       </c>
       <c r="D115" s="34" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E115" s="39"/>
       <c r="F115" s="38" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="G115" s="40" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="H115" s="42" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="I115" s="40" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="J115" s="42" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
       <c r="M115" s="1" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="N115" s="1"/>
       <c r="O115" s="2" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="S115" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="XED115" s="0"/>
     </row>
     <row r="116" customFormat="false" ht="54.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="B116" s="28" t="s">
         <v>33</v>
@@ -11336,24 +11280,24 @@
         <v>1</v>
       </c>
       <c r="D116" s="34" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E116" s="30"/>
       <c r="F116" s="10" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="G116" s="43" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="H116" s="43" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="I116" s="14"/>
       <c r="J116" s="14"/>
       <c r="K116" s="14"/>
       <c r="L116" s="30"/>
       <c r="M116" s="1" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="30" t="s">
@@ -11373,7 +11317,7 @@
     </row>
     <row r="117" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="10" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B117" s="28" t="s">
         <v>25</v>
@@ -11383,27 +11327,27 @@
         <v>1</v>
       </c>
       <c r="D117" s="34" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E117" s="30"/>
       <c r="F117" s="10" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="G117" s="43" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="H117" s="43" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I117" s="14"/>
       <c r="J117" s="14"/>
       <c r="K117" s="14"/>
       <c r="L117" s="30"/>
       <c r="M117" s="30" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="N117" s="8" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="O117" s="30"/>
       <c r="P117" s="30"/>
@@ -11420,7 +11364,7 @@
     </row>
     <row r="118" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="10" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="B118" s="28" t="s">
         <v>103</v>
@@ -11430,11 +11374,11 @@
         <v>1</v>
       </c>
       <c r="D118" s="34" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E118" s="30"/>
       <c r="F118" s="10" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="G118" s="28" t="s">
         <v>323</v>
@@ -11460,7 +11404,7 @@
     </row>
     <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="10" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="B119" s="28" t="s">
         <v>33</v>
@@ -11470,17 +11414,17 @@
         <v>1</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E119" s="30"/>
       <c r="F119" s="30" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="G119" s="28" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="H119" s="28" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="I119" s="14"/>
       <c r="J119" s="14"/>
@@ -11489,7 +11433,7 @@
       <c r="M119" s="30"/>
       <c r="N119" s="30"/>
       <c r="O119" s="30" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="P119" s="30"/>
       <c r="Q119" s="30"/>
@@ -11502,27 +11446,27 @@
     </row>
     <row r="120" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="10" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="B120" s="28" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C120" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D120" s="28" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E120" s="30"/>
       <c r="F120" s="30" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="G120" s="28" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="H120" s="28" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="I120" s="14"/>
       <c r="J120" s="14"/>
@@ -11531,7 +11475,7 @@
       <c r="M120" s="30"/>
       <c r="N120" s="30"/>
       <c r="O120" s="44" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="P120" s="30"/>
       <c r="Q120" s="30"/>
@@ -11547,7 +11491,7 @@
     </row>
     <row r="121" customFormat="false" ht="54.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="B121" s="28" t="s">
         <v>33</v>
@@ -11557,17 +11501,17 @@
         <v>1</v>
       </c>
       <c r="D121" s="28" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E121" s="30"/>
       <c r="F121" s="10" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="G121" s="43" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="H121" s="43" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="I121" s="14"/>
       <c r="J121" s="14"/>
@@ -11592,7 +11536,7 @@
     </row>
     <row r="122" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="10" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="B122" s="28" t="s">
         <v>25</v>
@@ -11602,27 +11546,27 @@
         <v>1</v>
       </c>
       <c r="D122" s="28" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E122" s="30"/>
       <c r="F122" s="10" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="G122" s="43" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="H122" s="43" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="I122" s="14"/>
       <c r="J122" s="14"/>
       <c r="K122" s="14"/>
       <c r="L122" s="30"/>
       <c r="M122" s="30" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="N122" s="8" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="O122" s="30"/>
       <c r="P122" s="30"/>
@@ -11639,27 +11583,27 @@
     </row>
     <row r="123" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="10" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="B123" s="28" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="C123" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D123" s="28" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E123" s="30"/>
       <c r="F123" s="30" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="G123" s="44" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="H123" s="44" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="I123" s="14"/>
       <c r="J123" s="14"/>
@@ -11667,7 +11611,7 @@
       <c r="L123" s="30"/>
       <c r="M123" s="30"/>
       <c r="N123" s="30" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="O123" s="30"/>
       <c r="P123" s="30"/>
@@ -11684,7 +11628,7 @@
     </row>
     <row r="124" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="34" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B124" s="32" t="s">
         <v>38</v>
@@ -11694,17 +11638,17 @@
         <v>1</v>
       </c>
       <c r="D124" s="28" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E124" s="30"/>
       <c r="F124" s="30" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="G124" s="44" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="H124" s="9" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="I124" s="14"/>
       <c r="J124" s="14"/>
@@ -11726,7 +11670,7 @@
     </row>
     <row r="125" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="10" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="B125" s="28" t="s">
         <v>82</v>
@@ -11736,29 +11680,29 @@
         <v>1</v>
       </c>
       <c r="D125" s="28" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E125" s="30"/>
       <c r="F125" s="30" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="G125" s="28" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="H125" s="28" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="I125" s="14"/>
       <c r="J125" s="14"/>
       <c r="K125" s="8" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="L125" s="30"/>
       <c r="M125" s="30" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="O125" s="30"/>
       <c r="P125" s="30"/>
@@ -11775,7 +11719,7 @@
     </row>
     <row r="126" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="10" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="B126" s="28" t="s">
         <v>82</v>
@@ -11785,29 +11729,29 @@
         <v>1</v>
       </c>
       <c r="D126" s="28" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E126" s="30"/>
       <c r="F126" s="30" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="G126" s="28" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="H126" s="28" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="I126" s="14"/>
       <c r="J126" s="14"/>
       <c r="K126" s="8" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="L126" s="30"/>
       <c r="M126" s="30" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="N126" s="10" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="O126" s="30"/>
       <c r="P126" s="30"/>
@@ -11824,27 +11768,27 @@
     </row>
     <row r="127" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="10" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="B127" s="28" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C127" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D127" s="28" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E127" s="30"/>
       <c r="F127" s="30" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="G127" s="44" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="H127" s="44" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="I127" s="14"/>
       <c r="J127" s="14"/>
@@ -11852,12 +11796,12 @@
       <c r="L127" s="30"/>
       <c r="M127" s="30"/>
       <c r="N127" s="30" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="O127" s="30"/>
       <c r="P127" s="30"/>
       <c r="Q127" s="44" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="R127" s="30"/>
       <c r="S127" s="28" t="b">
@@ -11871,7 +11815,7 @@
     </row>
     <row r="128" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="10" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="B128" s="28" t="s">
         <v>109</v>
@@ -11881,17 +11825,17 @@
         <v>1</v>
       </c>
       <c r="D128" s="28" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E128" s="30"/>
       <c r="F128" s="30" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="G128" s="44" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H128" s="44" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="I128" s="14"/>
       <c r="J128" s="14"/>
@@ -11899,7 +11843,7 @@
       <c r="L128" s="30"/>
       <c r="M128" s="30"/>
       <c r="N128" s="30" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="O128" s="30"/>
       <c r="P128" s="30"/>
@@ -11916,27 +11860,27 @@
     </row>
     <row r="129" customFormat="false" ht="59" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="10" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="B129" s="28" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C129" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D129" s="28" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E129" s="30"/>
       <c r="F129" s="30" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="G129" s="44" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="H129" s="44" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="I129" s="14"/>
       <c r="J129" s="14"/>
@@ -11944,12 +11888,12 @@
       <c r="L129" s="30"/>
       <c r="M129" s="30"/>
       <c r="N129" s="30" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="O129" s="30"/>
       <c r="P129" s="30"/>
       <c r="Q129" s="44" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="R129" s="30"/>
       <c r="S129" s="28" t="b">
@@ -11963,27 +11907,27 @@
     </row>
     <row r="130" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="10" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B130" s="28" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C130" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D130" s="28" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E130" s="30"/>
       <c r="F130" s="30" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="G130" s="44" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="H130" s="44" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="I130" s="14"/>
       <c r="J130" s="14"/>
@@ -11991,12 +11935,12 @@
       <c r="L130" s="30"/>
       <c r="M130" s="30"/>
       <c r="N130" s="30" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="O130" s="30"/>
       <c r="P130" s="30"/>
       <c r="Q130" s="44" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="R130" s="30"/>
       <c r="S130" s="28" t="n">
@@ -12010,27 +11954,27 @@
     </row>
     <row r="131" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="10" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B131" s="28" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C131" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D131" s="28" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E131" s="30"/>
       <c r="F131" s="30" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="G131" s="44" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="H131" s="44" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="I131" s="14"/>
       <c r="J131" s="14"/>
@@ -12038,12 +11982,12 @@
       <c r="L131" s="30"/>
       <c r="M131" s="30"/>
       <c r="N131" s="30" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="O131" s="30"/>
       <c r="P131" s="30"/>
       <c r="Q131" s="44" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="R131" s="30"/>
       <c r="S131" s="28" t="n">
@@ -12057,7 +12001,7 @@
     </row>
     <row r="132" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="10" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="B132" s="28" t="s">
         <v>33</v>
@@ -12067,17 +12011,17 @@
         <v>1</v>
       </c>
       <c r="D132" s="28" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E132" s="30"/>
       <c r="F132" s="30" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="G132" s="44" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="H132" s="44" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="I132" s="14"/>
       <c r="J132" s="14"/>
@@ -12085,7 +12029,7 @@
       <c r="L132" s="30"/>
       <c r="M132" s="30"/>
       <c r="N132" s="30" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="O132" s="30" t="s">
         <v>183</v>
@@ -12104,7 +12048,7 @@
     </row>
     <row r="133" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="10" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="B133" s="28" t="s">
         <v>103</v>
@@ -12114,17 +12058,17 @@
         <v>1</v>
       </c>
       <c r="D133" s="28" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E133" s="30"/>
       <c r="F133" s="10" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="G133" s="28" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="I133" s="14"/>
       <c r="J133" s="14"/>
@@ -12144,7 +12088,7 @@
     </row>
     <row r="134" customFormat="false" ht="116.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>38</v>
@@ -12154,16 +12098,16 @@
         <v>1</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="L134" s="46"/>
       <c r="M134" s="47"/>
@@ -12255,34 +12199,34 @@
   <sheetData>
     <row r="1" s="52" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="50" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="C1" s="50" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="E1" s="50" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="F1" s="50" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="D2" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E2" s="10" t="n">
         <v>1</v>
@@ -12295,10 +12239,10 @@
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="D3" s="53" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>2</v>
@@ -12311,13 +12255,13 @@
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="D4" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F4" s="10"/>
     </row>
@@ -12326,13 +12270,13 @@
         <v>127</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>1</v>
@@ -12345,10 +12289,10 @@
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>1</v>
@@ -12361,26 +12305,26 @@
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="D7" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="F7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D8" s="53" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>3</v>
@@ -12389,16 +12333,16 @@
     </row>
     <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D9" s="53" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>5</v>
@@ -12407,14 +12351,14 @@
     </row>
     <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>4</v>
@@ -12423,16 +12367,16 @@
     </row>
     <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>13</v>
@@ -12441,14 +12385,14 @@
     </row>
     <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>4</v>
@@ -12457,16 +12401,16 @@
     </row>
     <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D13" s="53" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>15</v>
@@ -12475,14 +12419,14 @@
     </row>
     <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D14" s="53" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>5</v>
@@ -12495,10 +12439,10 @@
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D15" s="53" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E15" s="10" t="n">
         <v>5</v>
@@ -12511,10 +12455,10 @@
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D16" s="53" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>6</v>
@@ -12524,14 +12468,14 @@
     </row>
     <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>11</v>
@@ -12544,10 +12488,10 @@
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D18" s="53" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>14</v>
@@ -12560,10 +12504,10 @@
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>15</v>
@@ -12575,16 +12519,16 @@
         <v>159</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D20" s="53" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="F20" s="10"/>
     </row>
@@ -12594,10 +12538,10 @@
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>15</v>
@@ -12610,10 +12554,10 @@
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>16</v>
@@ -12622,14 +12566,14 @@
     </row>
     <row r="23" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D23" s="53" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>16</v>
@@ -12638,32 +12582,32 @@
     </row>
     <row r="24" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D24" s="53" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="F24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D25" s="53" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>40</v>
@@ -12676,13 +12620,13 @@
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="10" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="D26" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F26" s="10"/>
     </row>
@@ -12691,13 +12635,13 @@
         <v>205</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="D27" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E27" s="49" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12705,16 +12649,16 @@
         <v>205</v>
       </c>
       <c r="B28" s="48" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C28" s="48" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="D28" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E28" s="49" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12722,16 +12666,16 @@
         <v>205</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="D29" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E29" s="49" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12739,13 +12683,13 @@
         <v>221</v>
       </c>
       <c r="C30" s="48" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="D30" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E30" s="49" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12753,16 +12697,16 @@
         <v>221</v>
       </c>
       <c r="B31" s="48" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C31" s="48" t="s">
+        <v>677</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>656</v>
+      </c>
+      <c r="E31" s="49" t="s">
         <v>682</v>
-      </c>
-      <c r="D31" s="53" t="s">
-        <v>661</v>
-      </c>
-      <c r="E31" s="49" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12770,16 +12714,16 @@
         <v>221</v>
       </c>
       <c r="B32" s="48" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C32" s="48" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="D32" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E32" s="49" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12787,13 +12731,13 @@
         <v>229</v>
       </c>
       <c r="C33" s="48" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="D33" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E33" s="48" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12801,16 +12745,16 @@
         <v>229</v>
       </c>
       <c r="B34" s="48" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C34" s="48" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="D34" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E34" s="48" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12818,16 +12762,16 @@
         <v>229</v>
       </c>
       <c r="B35" s="48" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C35" s="48" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="D35" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E35" s="48" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12835,16 +12779,16 @@
         <v>229</v>
       </c>
       <c r="B36" s="48" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C36" s="48" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="D36" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E36" s="48" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12852,16 +12796,16 @@
         <v>229</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C37" s="48" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="D37" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E37" s="48" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12869,16 +12813,16 @@
         <v>229</v>
       </c>
       <c r="B38" s="48" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C38" s="48" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="D38" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E38" s="48" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12889,35 +12833,35 @@
         <v>32</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E39" s="48" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="56" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="D40" s="57" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E40" s="58" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="56" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="C41" s="48" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="D41" s="53" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E41" s="48" t="n">
         <v>1</v>
@@ -12925,16 +12869,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="59" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="C42" s="48" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="D42" s="49" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E42" s="48" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12942,13 +12886,13 @@
         <v>263</v>
       </c>
       <c r="C43" s="48" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="D43" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E43" s="48" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12956,16 +12900,16 @@
         <v>263</v>
       </c>
       <c r="B44" s="48" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C44" s="48" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="D44" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E44" s="48" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12973,13 +12917,13 @@
         <v>173</v>
       </c>
       <c r="C45" s="48" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12987,13 +12931,13 @@
         <v>213</v>
       </c>
       <c r="C46" s="48" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="D46" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E46" s="49" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13001,44 +12945,44 @@
         <v>213</v>
       </c>
       <c r="B47" s="48" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C47" s="48" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="D47" s="53" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E47" s="49" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="30" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="D48" s="57" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E48" s="58" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="D49" s="49" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -13083,25 +13027,25 @@
         <v>3</v>
       </c>
       <c r="B1" s="61" t="s">
+        <v>695</v>
+      </c>
+      <c r="C1" s="60" t="s">
+        <v>696</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>697</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>698</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>699</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>700</v>
       </c>
-      <c r="C1" s="60" t="s">
+      <c r="H1" s="60" t="s">
         <v>701</v>
-      </c>
-      <c r="D1" s="60" t="s">
-        <v>702</v>
-      </c>
-      <c r="E1" s="60" t="s">
-        <v>703</v>
-      </c>
-      <c r="F1" s="60" t="s">
-        <v>704</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>705</v>
-      </c>
-      <c r="H1" s="60" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13109,13 +13053,13 @@
         <v>26</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="E2" s="48" t="b">
         <f aca="false">TRUE()</f>
@@ -13135,13 +13079,13 @@
         <v>107</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="E3" s="48" t="b">
         <f aca="false">TRUE()</f>
@@ -13158,16 +13102,16 @@
     </row>
     <row r="4" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="E4" s="48" t="b">
         <f aca="false">TRUE()</f>
@@ -13187,13 +13131,13 @@
         <v>268</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="E5" s="48" t="b">
         <f aca="false">FALSE()</f>
@@ -13208,7 +13152,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13216,13 +13160,13 @@
         <v>277</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="E6" s="48" t="b">
         <f aca="false">FALSE()</f>
@@ -13237,7 +13181,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13245,13 +13189,13 @@
         <v>328</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="E7" s="48" t="b">
         <f aca="false">FALSE()</f>
@@ -13263,21 +13207,21 @@
       </c>
       <c r="G7" s="48"/>
       <c r="H7" s="10" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="34" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="E8" s="48" t="b">
         <f aca="false">FALSE()</f>
@@ -13289,21 +13233,21 @@
       </c>
       <c r="G8" s="48"/>
       <c r="H8" s="10" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="34" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="E9" s="48" t="b">
         <f aca="false">FALSE()</f>
@@ -13318,21 +13262,21 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="34" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="E10" s="48" t="b">
         <f aca="false">FALSE()</f>
@@ -13347,21 +13291,21 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="E11" s="48" t="b">
         <f aca="false">TRUE()</f>
@@ -13378,16 +13322,16 @@
     </row>
     <row r="12" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="E12" s="48" t="b">
         <f aca="false">FALSE()</f>
@@ -13402,7 +13346,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
   </sheetData>
@@ -13434,10 +13378,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="63" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="B1" s="63" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="C1" s="63" t="s">
         <v>6</v>
@@ -13452,27 +13396,27 @@
         <v>9</v>
       </c>
       <c r="G1" s="63" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="H1" s="63" t="s">
         <v>12</v>
       </c>
       <c r="I1" s="62" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="65" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="C2" s="65" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="D2" s="65" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="E2" s="65"/>
       <c r="F2" s="65"/>
@@ -13481,16 +13425,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="65" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="B3" s="65" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C3" s="65" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="D3" s="65" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="E3" s="65"/>
       <c r="F3" s="65"/>
@@ -13505,10 +13449,10 @@
         <v>161</v>
       </c>
       <c r="C4" s="65" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="D4" s="65" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="E4" s="65"/>
       <c r="F4" s="65"/>
@@ -13517,16 +13461,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="65" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="B5" s="65" t="s">
         <v>161</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="E5" s="65"/>
       <c r="F5" s="65"/>
@@ -13535,16 +13479,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="65" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="B6" s="65" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="D6" s="65" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="E6" s="65"/>
       <c r="F6" s="65"/>
@@ -13553,16 +13497,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="65" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="B7" s="65" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="D7" s="65" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
@@ -13579,7 +13523,7 @@
       <c r="E8" s="65"/>
       <c r="F8" s="65"/>
       <c r="G8" s="65" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="H8" s="65"/>
     </row>
@@ -13593,7 +13537,7 @@
       <c r="E9" s="65"/>
       <c r="F9" s="65"/>
       <c r="G9" s="65" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="H9" s="65"/>
     </row>
@@ -13621,7 +13565,7 @@
       <c r="E11" s="65"/>
       <c r="F11" s="65"/>
       <c r="G11" s="65" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="H11" s="65"/>
     </row>
@@ -13635,7 +13579,7 @@
       <c r="E12" s="65"/>
       <c r="F12" s="65"/>
       <c r="G12" s="65" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="H12" s="65"/>
     </row>
@@ -13649,7 +13593,7 @@
       <c r="E13" s="65"/>
       <c r="F13" s="65"/>
       <c r="G13" s="65" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="H13" s="65"/>
       <c r="I13" s="62"/>
@@ -13664,7 +13608,7 @@
       <c r="E14" s="65"/>
       <c r="F14" s="65"/>
       <c r="G14" s="65" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="H14" s="65"/>
       <c r="I14" s="62"/>
@@ -13674,13 +13618,13 @@
         <v>133</v>
       </c>
       <c r="B15" s="65" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="C15" s="65" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="D15" s="65" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="E15" s="65"/>
       <c r="F15" s="65"/>
@@ -13692,13 +13636,13 @@
         <v>133</v>
       </c>
       <c r="B16" s="65" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="C16" s="65" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="D16" s="65" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="E16" s="65"/>
       <c r="F16" s="65"/>
@@ -13715,7 +13659,7 @@
       <c r="E17" s="65"/>
       <c r="F17" s="65"/>
       <c r="G17" s="65" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="H17" s="65"/>
     </row>
@@ -13724,13 +13668,13 @@
         <v>139</v>
       </c>
       <c r="B18" s="65" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="C18" s="65" t="s">
+        <v>752</v>
+      </c>
+      <c r="D18" s="65" t="s">
         <v>757</v>
-      </c>
-      <c r="D18" s="65" t="s">
-        <v>762</v>
       </c>
       <c r="E18" s="65"/>
       <c r="F18" s="65"/>
@@ -13742,13 +13686,13 @@
         <v>139</v>
       </c>
       <c r="B19" s="65" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="C19" s="65" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="D19" s="65" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="E19" s="65"/>
       <c r="F19" s="65"/>
@@ -13763,10 +13707,10 @@
         <v>141</v>
       </c>
       <c r="C20" s="65" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="D20" s="65" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="E20" s="65"/>
       <c r="F20" s="65"/>
@@ -13783,7 +13727,7 @@
       <c r="E21" s="65"/>
       <c r="F21" s="65"/>
       <c r="G21" s="65" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="H21" s="65"/>
     </row>
@@ -13792,13 +13736,13 @@
         <v>148</v>
       </c>
       <c r="B22" s="65" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="C22" s="65" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="D22" s="65" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="E22" s="65"/>
       <c r="F22" s="65"/>
@@ -13810,13 +13754,13 @@
         <v>148</v>
       </c>
       <c r="B23" s="65" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="C23" s="65" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="D23" s="65" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="E23" s="65"/>
       <c r="F23" s="65"/>
@@ -13833,7 +13777,7 @@
       <c r="E24" s="65"/>
       <c r="F24" s="65"/>
       <c r="G24" s="65" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="H24" s="65"/>
     </row>
@@ -13842,13 +13786,13 @@
         <v>154</v>
       </c>
       <c r="B25" s="65" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="C25" s="65" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="D25" s="65" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="E25" s="65"/>
       <c r="F25" s="65"/>
@@ -13860,13 +13804,13 @@
         <v>154</v>
       </c>
       <c r="B26" s="65" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="C26" s="65" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="D26" s="65" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="E26" s="65"/>
       <c r="F26" s="65"/>
@@ -13883,7 +13827,7 @@
       <c r="E27" s="65"/>
       <c r="F27" s="65"/>
       <c r="G27" s="65" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="H27" s="65"/>
     </row>
@@ -13892,19 +13836,19 @@
         <v>156</v>
       </c>
       <c r="B28" s="65" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C28" s="65" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="D28" s="65" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="E28" s="65"/>
       <c r="F28" s="65"/>
       <c r="G28" s="65"/>
       <c r="H28" s="65" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13912,19 +13856,19 @@
         <v>156</v>
       </c>
       <c r="B29" s="65" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="C29" s="65" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="D29" s="65" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="E29" s="65"/>
       <c r="F29" s="65"/>
       <c r="G29" s="65"/>
       <c r="H29" s="65" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13932,19 +13876,19 @@
         <v>156</v>
       </c>
       <c r="B30" s="65" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="C30" s="65" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="D30" s="65" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="E30" s="65"/>
       <c r="F30" s="65"/>
       <c r="G30" s="65"/>
       <c r="H30" s="65" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13952,19 +13896,19 @@
         <v>156</v>
       </c>
       <c r="B31" s="65" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="C31" s="65" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="D31" s="65" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="E31" s="65"/>
       <c r="F31" s="65"/>
       <c r="G31" s="65"/>
       <c r="H31" s="65" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13972,19 +13916,19 @@
         <v>156</v>
       </c>
       <c r="B32" s="65" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="C32" s="65" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="D32" s="65" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="E32" s="65"/>
       <c r="F32" s="65"/>
       <c r="G32" s="65"/>
       <c r="H32" s="65" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13992,13 +13936,13 @@
         <v>156</v>
       </c>
       <c r="B33" s="65" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="C33" s="65" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="D33" s="65" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="E33" s="65"/>
       <c r="F33" s="65"/>
@@ -14026,20 +13970,20 @@
         <v>162</v>
       </c>
       <c r="B35" s="65" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="C35" s="65" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="E35" s="65"/>
       <c r="F35" s="65"/>
       <c r="G35" s="65"/>
       <c r="H35" s="65"/>
       <c r="I35" s="62" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14047,20 +13991,20 @@
         <v>162</v>
       </c>
       <c r="B36" s="65" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="C36" s="65" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="E36" s="65"/>
       <c r="F36" s="65"/>
       <c r="G36" s="65"/>
       <c r="H36" s="65"/>
       <c r="I36" s="62" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14068,20 +14012,20 @@
         <v>162</v>
       </c>
       <c r="B37" s="65" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="C37" s="65" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="D37" s="65" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="E37" s="65"/>
       <c r="F37" s="65"/>
       <c r="G37" s="65"/>
       <c r="H37" s="65"/>
       <c r="I37" s="62" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14089,20 +14033,20 @@
         <v>162</v>
       </c>
       <c r="B38" s="65" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="C38" s="65" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="D38" s="65" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="E38" s="65"/>
       <c r="F38" s="65"/>
       <c r="G38" s="65"/>
       <c r="H38" s="65"/>
       <c r="I38" s="62" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14110,20 +14054,20 @@
         <v>162</v>
       </c>
       <c r="B39" s="65" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="C39" s="65" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="D39" s="65" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="E39" s="65"/>
       <c r="F39" s="65"/>
       <c r="G39" s="65"/>
       <c r="H39" s="65"/>
       <c r="I39" s="62" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14131,19 +14075,19 @@
         <v>162</v>
       </c>
       <c r="B40" s="65" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C40" s="65" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D40" s="65" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E40" s="65"/>
       <c r="F40" s="65"/>
       <c r="G40" s="65"/>
       <c r="H40" s="65" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14151,13 +14095,13 @@
         <v>162</v>
       </c>
       <c r="B41" s="65" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="C41" s="65" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="D41" s="65" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="E41" s="65"/>
       <c r="F41" s="65"/>
@@ -14169,13 +14113,13 @@
         <v>162</v>
       </c>
       <c r="B42" s="65" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="C42" s="65" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="D42" s="65" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="E42" s="65"/>
       <c r="F42" s="65"/>
@@ -14187,13 +14131,13 @@
         <v>162</v>
       </c>
       <c r="B43" s="67" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="C43" s="65" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="D43" s="65" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="E43" s="65"/>
       <c r="F43" s="65"/>
@@ -14205,13 +14149,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="65" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="C44" s="65" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="D44" s="65" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="E44" s="65"/>
       <c r="F44" s="65"/>
@@ -14223,13 +14167,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="65" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="C45" s="65" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="D45" s="65" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="E45" s="65"/>
       <c r="F45" s="65"/>
@@ -14244,10 +14188,10 @@
         <v>161</v>
       </c>
       <c r="C46" s="65" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="D46" s="65" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="E46" s="65"/>
       <c r="F46" s="65"/>
@@ -14259,13 +14203,13 @@
         <v>162</v>
       </c>
       <c r="B47" s="65" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="C47" s="65" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="D47" s="65" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
@@ -14282,7 +14226,7 @@
       <c r="E48" s="65"/>
       <c r="F48" s="65"/>
       <c r="G48" s="65" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="H48" s="65"/>
     </row>
@@ -14291,13 +14235,13 @@
         <v>198</v>
       </c>
       <c r="B49" s="65" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="C49" s="65" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="D49" s="65" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="E49" s="65"/>
       <c r="F49" s="65"/>
@@ -14309,13 +14253,13 @@
         <v>198</v>
       </c>
       <c r="B50" s="65" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="C50" s="65" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="D50" s="65" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="E50" s="65"/>
       <c r="F50" s="65"/>
@@ -14332,7 +14276,7 @@
       <c r="E51" s="65"/>
       <c r="F51" s="65"/>
       <c r="G51" s="65" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="H51" s="65"/>
     </row>
@@ -14341,13 +14285,13 @@
         <v>206</v>
       </c>
       <c r="B52" s="65" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="C52" s="65" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="D52" s="65" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="E52" s="65"/>
       <c r="F52" s="65"/>
@@ -14359,13 +14303,13 @@
         <v>206</v>
       </c>
       <c r="B53" s="65" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="C53" s="65" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="D53" s="65" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="E53" s="65"/>
       <c r="F53" s="65"/>
@@ -14377,13 +14321,13 @@
         <v>206</v>
       </c>
       <c r="B54" s="65" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="C54" s="65" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="D54" s="65" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="E54" s="65"/>
       <c r="F54" s="65"/>
@@ -14395,13 +14339,13 @@
         <v>206</v>
       </c>
       <c r="B55" s="65" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="C55" s="65" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="D55" s="65" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="E55" s="65"/>
       <c r="F55" s="65"/>
@@ -14413,13 +14357,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="65" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="C56" s="65" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="D56" s="65" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="E56" s="65"/>
       <c r="F56" s="65"/>
@@ -14431,13 +14375,13 @@
         <v>222</v>
       </c>
       <c r="B57" s="62" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="C57" s="62" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="D57" s="62" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14445,13 +14389,13 @@
         <v>222</v>
       </c>
       <c r="B58" s="62" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="C58" s="62" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="D58" s="62" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14459,357 +14403,357 @@
         <v>222</v>
       </c>
       <c r="B59" s="62" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="C59" s="62" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="D59" s="62" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="66" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="B60" s="62" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="C60" s="62" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="D60" s="62" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="66" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="B61" s="62" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="C61" s="62" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D61" s="62" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="66" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="B62" s="62" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="C62" s="62" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="D62" s="62" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="66" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="B63" s="62" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="C63" s="62" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="D63" s="62" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="62" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B64" s="62" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="C64" s="62" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="D64" s="62" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="62" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B65" s="67" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C65" s="67" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="D65" s="67" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="E65" s="67"/>
       <c r="F65" s="67"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="62" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B66" s="67" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="C66" s="67" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="D66" s="67" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="E66" s="67"/>
       <c r="F66" s="67"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="62" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B67" s="67" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="C67" s="67" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="D67" s="67" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="E67" s="67"/>
       <c r="F67" s="67"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="62" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B68" s="67" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="C68" s="67" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="D68" s="67" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="E68" s="67"/>
       <c r="F68" s="67"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="62" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B69" s="67" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="C69" s="67" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="D69" s="67" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="E69" s="67"/>
       <c r="F69" s="67"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="62" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B70" s="67" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="C70" s="67" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="D70" s="67" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="E70" s="67"/>
       <c r="F70" s="67"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="62" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B71" s="67" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C71" s="67" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="D71" s="67" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="E71" s="67"/>
       <c r="F71" s="67"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="62" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B72" s="67" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="C72" s="67" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="D72" s="67" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="E72" s="67"/>
       <c r="F72" s="67"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="62" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B73" s="67" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="C73" s="67" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="D73" s="67" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="E73" s="67"/>
       <c r="F73" s="67"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="62" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B74" s="67" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="C74" s="67" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="D74" s="67" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="E74" s="67"/>
       <c r="F74" s="67"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="62" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B75" s="67" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="C75" s="67" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="D75" s="67" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="E75" s="67"/>
       <c r="F75" s="67"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="62" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B76" s="62" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="C76" s="62" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="D76" s="62" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="62" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B77" s="62" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="C77" s="62" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="D77" s="62" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="62" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B78" s="62" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="C78" s="62" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="D78" s="62" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="68" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B79" s="67" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="C79" s="62" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="D79" s="62" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="68" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B80" s="62" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="C80" s="62" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="D80" s="62" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="68" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B81" s="62" t="s">
         <v>161</v>
       </c>
       <c r="C81" s="62" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="D81" s="62" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="68" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B82" s="62" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="C82" s="67" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="D82" s="67" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="E82" s="67"/>
       <c r="F82" s="67"/>
@@ -14819,16 +14763,16 @@
         <v>320</v>
       </c>
       <c r="B83" s="62" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="C83" s="70" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="D83" s="62" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="H83" s="67" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14836,13 +14780,13 @@
         <v>320</v>
       </c>
       <c r="B84" s="62" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="C84" s="67" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="D84" s="70" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="E84" s="70"/>
       <c r="F84" s="70"/>
@@ -14855,13 +14799,13 @@
         <v>320</v>
       </c>
       <c r="B85" s="62" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="C85" s="67" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="D85" s="62" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14869,13 +14813,13 @@
         <v>320</v>
       </c>
       <c r="B86" s="62" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="C86" s="67" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="D86" s="67" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="E86" s="67"/>
       <c r="F86" s="67"/>
@@ -14885,13 +14829,13 @@
         <v>320</v>
       </c>
       <c r="B87" s="62" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="C87" s="67" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="D87" s="67" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="E87" s="67"/>
       <c r="F87" s="67"/>
@@ -14901,13 +14845,13 @@
         <v>320</v>
       </c>
       <c r="B88" s="62" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="C88" s="67" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="D88" s="67" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="E88" s="67"/>
       <c r="F88" s="67"/>
@@ -14920,13 +14864,13 @@
         <v>320</v>
       </c>
       <c r="B89" s="62" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="C89" s="67" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="D89" s="67" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="E89" s="67"/>
       <c r="F89" s="67"/>
@@ -14936,13 +14880,13 @@
         <v>320</v>
       </c>
       <c r="B90" s="62" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C90" s="67" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="D90" s="67" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="E90" s="67"/>
       <c r="F90" s="67"/>
@@ -14958,276 +14902,276 @@
         <v>161</v>
       </c>
       <c r="C91" s="67" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="D91" s="62" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="69" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="B92" s="62" t="s">
         <v>26</v>
       </c>
       <c r="C92" s="62" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="D92" s="62" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="69" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="B93" s="62" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="C93" s="62" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="D93" s="62" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="H93" s="62" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="69" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="B94" s="62" t="s">
         <v>161</v>
       </c>
       <c r="C94" s="62" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="D94" s="62" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="69" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="B95" s="67" t="s">
+        <v>925</v>
+      </c>
+      <c r="C95" s="67" t="s">
+        <v>926</v>
+      </c>
+      <c r="D95" s="67" t="s">
+        <v>927</v>
+      </c>
+      <c r="E95" s="67" t="s">
+        <v>928</v>
+      </c>
+      <c r="F95" s="67" t="s">
+        <v>929</v>
+      </c>
+      <c r="H95" s="62" t="s">
         <v>930</v>
-      </c>
-      <c r="C95" s="67" t="s">
-        <v>931</v>
-      </c>
-      <c r="D95" s="67" t="s">
-        <v>932</v>
-      </c>
-      <c r="E95" s="67" t="s">
-        <v>933</v>
-      </c>
-      <c r="F95" s="67" t="s">
-        <v>934</v>
-      </c>
-      <c r="H95" s="62" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="69" t="s">
+        <v>931</v>
+      </c>
+      <c r="B96" s="62" t="s">
+        <v>932</v>
+      </c>
+      <c r="C96" s="67" t="s">
+        <v>933</v>
+      </c>
+      <c r="D96" s="67" t="s">
+        <v>934</v>
+      </c>
+      <c r="E96" s="67" t="s">
+        <v>935</v>
+      </c>
+      <c r="F96" s="67" t="s">
         <v>936</v>
-      </c>
-      <c r="B96" s="62" t="s">
-        <v>937</v>
-      </c>
-      <c r="C96" s="67" t="s">
-        <v>938</v>
-      </c>
-      <c r="D96" s="67" t="s">
-        <v>939</v>
-      </c>
-      <c r="E96" s="67" t="s">
-        <v>940</v>
-      </c>
-      <c r="F96" s="67" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="69" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="B97" s="62" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="C97" s="67" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="D97" s="67" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="E97" s="67" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="F97" s="67" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="69" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="B98" s="62" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C98" s="62" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="D98" s="62" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="69" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B99" s="67" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="C99" s="67" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="D99" s="67" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="69" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B100" s="67" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="C100" s="67" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="D100" s="67" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="69" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B101" s="67" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="C101" s="67" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="D101" s="67" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="69" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B102" s="67" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="C102" s="67" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="D102" s="67" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="69" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="G103" s="65" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="69" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="G104" s="65" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="69" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B105" s="67" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="C105" s="67" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="D105" s="67" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="69" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B106" s="67" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="C106" s="67" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="D106" s="67" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="69" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B107" s="67" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="C107" s="67" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="D107" s="67" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="69" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B108" s="67" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="C108" s="67" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="D108" s="67" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="69" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="G109" s="65" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="69" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="G110" s="65" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15235,13 +15179,13 @@
         <v>175</v>
       </c>
       <c r="B111" s="67" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="C111" s="62" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="D111" s="62" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15249,13 +15193,13 @@
         <v>175</v>
       </c>
       <c r="B112" s="62" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="C112" s="62" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="D112" s="62" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15263,13 +15207,13 @@
         <v>175</v>
       </c>
       <c r="B113" s="67" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="C113" s="62" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="D113" s="62" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15277,13 +15221,13 @@
         <v>175</v>
       </c>
       <c r="B114" s="67" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="C114" s="62" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="D114" s="62" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15291,13 +15235,13 @@
         <v>175</v>
       </c>
       <c r="B115" s="67" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="C115" s="62" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="D115" s="62" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15305,13 +15249,13 @@
         <v>175</v>
       </c>
       <c r="B116" s="67" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="C116" s="62" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="D116" s="62" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15319,108 +15263,108 @@
         <v>175</v>
       </c>
       <c r="G117" s="65" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="66" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="B118" s="65" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="C118" s="65" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="D118" s="65" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="E118" s="65" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="F118" s="65" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="G118" s="66"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="66" t="s">
+        <v>981</v>
+      </c>
+      <c r="B119" s="65" t="s">
+        <v>685</v>
+      </c>
+      <c r="C119" s="65" t="s">
         <v>986</v>
       </c>
-      <c r="B119" s="65" t="s">
-        <v>690</v>
-      </c>
-      <c r="C119" s="65" t="s">
-        <v>991</v>
-      </c>
       <c r="D119" s="65" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="E119" s="65" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="F119" s="65" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="66" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="B120" s="65" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="C120" s="65" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="D120" s="65" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="E120" s="65" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F120" s="65" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="66" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="B121" s="65" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="C121" s="65" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="D121" s="65" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="E121" s="65" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="F121" s="65" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="66" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="B122" s="65" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="C122" s="65" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="D122" s="65" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="E122" s="65" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="F122" s="65" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -15459,63 +15403,63 @@
   <sheetData>
     <row r="1" s="73" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="72" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B1" s="72" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C1" s="72" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D1" s="72" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E1" s="72" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F1" s="72" t="s">
         <v>1007</v>
       </c>
-      <c r="B1" s="72" t="s">
+      <c r="G1" s="72" t="s">
         <v>1008</v>
       </c>
-      <c r="C1" s="72" t="s">
+      <c r="H1" s="72" t="s">
         <v>1009</v>
       </c>
-      <c r="D1" s="72" t="s">
+      <c r="I1" s="72" t="s">
         <v>1010</v>
       </c>
-      <c r="E1" s="72" t="s">
+      <c r="J1" s="72" t="s">
         <v>1011</v>
       </c>
-      <c r="F1" s="72" t="s">
+      <c r="K1" s="72" t="s">
         <v>1012</v>
       </c>
-      <c r="G1" s="72" t="s">
+      <c r="L1" s="73" t="s">
         <v>1013</v>
-      </c>
-      <c r="H1" s="72" t="s">
-        <v>1014</v>
-      </c>
-      <c r="I1" s="72" t="s">
-        <v>1015</v>
-      </c>
-      <c r="J1" s="72" t="s">
-        <v>1016</v>
-      </c>
-      <c r="K1" s="72" t="s">
-        <v>1017</v>
-      </c>
-      <c r="L1" s="73" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="44" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="B2" s="44" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F2" s="44" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G2" s="44" t="s">
         <v>1019</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D2" s="44" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F2" s="44" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G2" s="44" t="s">
-        <v>1024</v>
       </c>
       <c r="H2" s="44" t="n">
         <v>-10</v>
@@ -15524,36 +15468,36 @@
         <v>100</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="44" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="B3" s="44" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D3" s="74" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E3" s="74" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F3" s="74" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G3" s="44" t="s">
         <v>1027</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D3" s="74" t="s">
-        <v>1029</v>
-      </c>
-      <c r="E3" s="74" t="s">
-        <v>1030</v>
-      </c>
-      <c r="F3" s="74" t="s">
-        <v>1031</v>
-      </c>
-      <c r="G3" s="44" t="s">
-        <v>1032</v>
       </c>
       <c r="H3" s="44" t="n">
         <v>-10</v>
@@ -15562,36 +15506,36 @@
         <v>100</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="44" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B4" s="44" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E4" s="44" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F4" s="44" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G4" s="44" t="s">
         <v>1034</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>1035</v>
-      </c>
-      <c r="D4" s="44" t="s">
-        <v>1036</v>
-      </c>
-      <c r="E4" s="44" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F4" s="44" t="s">
-        <v>1038</v>
-      </c>
-      <c r="G4" s="44" t="s">
-        <v>1039</v>
       </c>
       <c r="H4" s="44" t="n">
         <v>-10</v>
@@ -15600,36 +15544,36 @@
         <v>100</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="D5" s="44" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="G5" s="44" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="H5" s="44" t="n">
         <v>-10</v>
@@ -15638,13 +15582,13 @@
         <v>100</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -15698,13 +15642,13 @@
         <v>107</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -15714,184 +15658,184 @@
         <v>107</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="E4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15899,19 +15843,19 @@
         <v>328</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15919,19 +15863,19 @@
         <v>328</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15939,19 +15883,19 @@
         <v>328</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15959,19 +15903,19 @@
         <v>328</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15979,19 +15923,19 @@
         <v>328</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15999,19 +15943,19 @@
         <v>328</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16019,13 +15963,13 @@
         <v>328</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16033,13 +15977,13 @@
         <v>328</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16047,13 +15991,13 @@
         <v>328</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16061,13 +16005,13 @@
         <v>328</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16075,19 +16019,19 @@
         <v>328</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16095,13 +16039,13 @@
         <v>328</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16109,13 +16053,13 @@
         <v>328</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16123,13 +16067,13 @@
         <v>328</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16137,13 +16081,13 @@
         <v>328</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16151,13 +16095,13 @@
         <v>328</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16165,13 +16109,13 @@
         <v>328</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16179,13 +16123,13 @@
         <v>328</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16193,13 +16137,13 @@
         <v>328</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16207,13 +16151,13 @@
         <v>328</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>1156</v>
+        <v>1151</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16221,13 +16165,13 @@
         <v>328</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16235,13 +16179,13 @@
         <v>328</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16249,13 +16193,13 @@
         <v>328</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16263,13 +16207,13 @@
         <v>328</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16277,13 +16221,13 @@
         <v>328</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16291,13 +16235,13 @@
         <v>328</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16305,13 +16249,13 @@
         <v>328</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16319,13 +16263,13 @@
         <v>328</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16333,13 +16277,13 @@
         <v>328</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16347,13 +16291,13 @@
         <v>328</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16361,13 +16305,13 @@
         <v>328</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16375,13 +16319,13 @@
         <v>328</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16389,19 +16333,19 @@
         <v>328</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16409,19 +16353,19 @@
         <v>328</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16429,19 +16373,19 @@
         <v>328</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16449,19 +16393,19 @@
         <v>328</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16469,19 +16413,19 @@
         <v>328</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16489,19 +16433,19 @@
         <v>328</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>1219</v>
+        <v>1214</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16509,19 +16453,19 @@
         <v>328</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16529,19 +16473,19 @@
         <v>328</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16549,13 +16493,13 @@
         <v>107</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16563,13 +16507,13 @@
         <v>107</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>1237</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16577,13 +16521,13 @@
         <v>107</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1238</v>
+        <v>1233</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16591,13 +16535,13 @@
         <v>107</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1241</v>
+        <v>1236</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16605,13 +16549,13 @@
         <v>107</v>
       </c>
       <c r="B60" s="75" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16619,13 +16563,13 @@
         <v>107</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16633,13 +16577,13 @@
         <v>107</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>1251</v>
+        <v>1246</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16647,19 +16591,19 @@
         <v>107</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1255</v>
+        <v>1250</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16667,13 +16611,13 @@
         <v>107</v>
       </c>
       <c r="B64" s="34" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
       <c r="D64" s="75" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
@@ -16683,13 +16627,13 @@
         <v>107</v>
       </c>
       <c r="B65" s="34" t="s">
-        <v>1261</v>
+        <v>1256</v>
       </c>
       <c r="C65" s="34" t="s">
-        <v>1262</v>
+        <v>1257</v>
       </c>
       <c r="D65" s="75" t="s">
-        <v>1263</v>
+        <v>1258</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
@@ -16699,13 +16643,13 @@
         <v>328</v>
       </c>
       <c r="B66" s="59" t="s">
-        <v>1264</v>
+        <v>1259</v>
       </c>
       <c r="C66" s="59" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="D66" s="59" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="E66" s="59"/>
       <c r="F66" s="59"/>
@@ -16715,13 +16659,13 @@
         <v>328</v>
       </c>
       <c r="B67" s="59" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="C67" s="59" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="D67" s="59" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="E67" s="59"/>
       <c r="F67" s="59"/>
@@ -16731,13 +16675,13 @@
         <v>328</v>
       </c>
       <c r="B68" s="59" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
       <c r="C68" s="59" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="D68" s="59" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="E68" s="59"/>
       <c r="F68" s="59"/>
@@ -16747,121 +16691,121 @@
         <v>328</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>1267</v>
+        <v>1262</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B70" s="59" t="s">
-        <v>1268</v>
+        <v>1263</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B71" s="59" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B72" s="59" t="s">
-        <v>1270</v>
+        <v>1265</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="E72" s="10"/>
       <c r="F72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B73" s="59" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="E73" s="10"/>
       <c r="F73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B74" s="59" t="s">
-        <v>1276</v>
+        <v>1271</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
       <c r="E74" s="10"/>
       <c r="F74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="30" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>1280</v>
+        <v>1275</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>1281</v>
+        <v>1276</v>
       </c>
       <c r="E75" s="10"/>
       <c r="F75" s="10"/>
@@ -16871,13 +16815,13 @@
         <v>328</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16885,13 +16829,13 @@
         <v>328</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16899,13 +16843,13 @@
         <v>328</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16913,13 +16857,13 @@
         <v>328</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16927,19 +16871,19 @@
         <v>107</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16947,19 +16891,19 @@
         <v>107</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16967,19 +16911,19 @@
         <v>107</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16987,19 +16931,19 @@
         <v>107</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17007,19 +16951,19 @@
         <v>107</v>
       </c>
       <c r="B84" s="20" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17027,19 +16971,19 @@
         <v>277</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17047,425 +16991,425 @@
         <v>277</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>1322</v>
+        <v>1317</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1344</v>
+        <v>1339</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1358</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>1369</v>
+        <v>1364</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>1381</v>
+        <v>1376</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1382</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1386</v>
+        <v>1381</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
     </row>
   </sheetData>

--- a/survey/references/OD_nationale_quebec_2025.xlsx
+++ b/survey/references/OD_nationale_quebec_2025.xlsx
@@ -2278,7 +2278,7 @@
     <t xml:space="preserve">household.income</t>
   </si>
   <si>
-    <t xml:space="preserve">Tranche de revenu avant impôts (brut) du ménage, en 2024?
+    <t xml:space="preserve">Tranche de revenu avant impôts (brut) du ménage, en 2025?
 __Facultatif__</t>
   </si>
   <si>
@@ -2291,7 +2291,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">What was your household's income range before taxes (gross income), in 2024?
+      <t xml:space="preserve">What was your household's income range before taxes (gross income), in 2025?
 </t>
     </r>
     <r>
